--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9256806125</v>
+        <v>46157.93097517785</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93097517785</v>
+        <v>46157.93172474916</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93172474916</v>
+        <v>46157.93399840293</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93399840293</v>
+        <v>46157.93717793429</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93717793429</v>
+        <v>46158.28216160302</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28216160302</v>
+        <v>46158.29680934455</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29680934455</v>
+        <v>46158.29814486602</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29814486602</v>
+        <v>46158.33387208451</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33387208451</v>
+        <v>46158.36856927942</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/6. ООО Автоград Гарант/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36856927942</v>
+        <v>46158.37287673566</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
